--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484235_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484235_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5082</v>
+        <v>0.6944</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0502</v>
+        <v>1.7596</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.542</v>
+        <v>-1.0652</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.6729</v>
+        <v>0.499</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.8634</v>
+        <v>0.7693</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8095</v>
+        <v>-0.2702</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5708</v>
+        <v>1.6577</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6817</v>
+        <v>1.6577</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8891</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.2437</v>
+        <v>-1.1587</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.5451</v>
+        <v>-0.8885</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.6986</v>
+        <v>-0.2702</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3532</v>
+        <v>-0.3907</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9137</v>
+        <v>0.1018</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4395</v>
+        <v>-0.4925</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5424</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.181</v>
+        <v>0.2216</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3551</v>
+        <v>0.0013</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1741</v>
+        <v>0.2203</v>
       </c>
       <c r="G3" t="n">
-        <v>0.499</v>
+        <v>0.3173</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7693</v>
+        <v>0.142</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2702</v>
+        <v>0.1753</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6577</v>
+        <v>0.1223</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6577</v>
+        <v>0.0819</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1587</v>
+        <v>0.1949</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8885</v>
+        <v>0.0601</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2702</v>
+        <v>0.1348</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9041</v>
+        <v>-0.0138</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3026</v>
+        <v>-0.121</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6015</v>
+        <v>0.1073</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1127</v>
+        <v>0.2111</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0013</v>
+        <v>1.6635</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1114</v>
+        <v>-1.4524</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3173</v>
+        <v>1.0714</v>
       </c>
       <c r="H4" t="n">
-        <v>0.142</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1753</v>
+        <v>0.998</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1223</v>
+        <v>2.6395</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0819</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0405</v>
+        <v>1.9424</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1949</v>
+        <v>-1.568</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0601</v>
+        <v>-0.6237</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1348</v>
+        <v>-0.9443</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1227</v>
+        <v>0.1396</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>0.0007</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0017</v>
+        <v>0.1389</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1195</v>
+        <v>0.0382</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3601</v>
+        <v>6.3623</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4796</v>
+        <v>-6.3241</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0714</v>
+        <v>-2.6729</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07340000000000001</v>
+        <v>-1.8634</v>
       </c>
       <c r="I5" t="n">
-        <v>0.998</v>
+        <v>-0.8095</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6395</v>
+        <v>2.5708</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.6817</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9424</v>
+        <v>1.8891</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.568</v>
+        <v>-5.2437</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6237</v>
+        <v>-2.5451</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9443</v>
+        <v>-2.6986</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.191</v>
+        <v>0.8832</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3026</v>
+        <v>0.2258</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1117</v>
+        <v>0.6574</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6093</v>
+        <v>1.8279</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>4.5424</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6093</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3721</v>
+        <v>-0.1008</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7506</v>
+        <v>0.0237</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.1227</v>
+        <v>-0.1246</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.8816</v>
+        <v>-0.5266</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4805</v>
+        <v>0.2829</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4011</v>
+        <v>-0.8095</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2223</v>
+        <v>0.023</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1946</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0276</v>
+        <v>-0.6741</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.1038</v>
+        <v>-0.5496</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.6751</v>
+        <v>-0.4142</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4287</v>
+        <v>-0.1354</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9438</v>
+        <v>-0.3556</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4435</v>
+        <v>0.0007</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5003</v>
+        <v>-0.3564</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.9917</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6553</v>
+        <v>-0.6303</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3401</v>
+        <v>-0.3939</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3152</v>
+        <v>-0.2363</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5266</v>
+        <v>-1.7838</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2829</v>
+        <v>-1.2978</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8095</v>
+        <v>-0.486</v>
       </c>
       <c r="J7" t="n">
-        <v>0.023</v>
+        <v>-0.066</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6971000000000001</v>
+        <v>-0.1203</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6741</v>
+        <v>0.0543</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5496</v>
+        <v>-1.7178</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4142</v>
+        <v>-1.1775</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1354</v>
+        <v>-0.5403</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9101</v>
+        <v>-0.0186</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3631</v>
+        <v>-0.328</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.547</v>
+        <v>0.3094</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.387</v>
+        <v>-2.1073</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.96</v>
+        <v>-1.5492</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.427</v>
+        <v>-0.5581</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7838</v>
+        <v>-1.3328</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2978</v>
+        <v>-0.3888</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.486</v>
+        <v>-0.9439</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.066</v>
+        <v>-0.6536</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1203</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0543</v>
+        <v>-0.6741</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7178</v>
+        <v>-0.6792</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1775</v>
+        <v>-0.4093</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5403</v>
+        <v>-0.2698</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7753</v>
+        <v>0.2022</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8941</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1187</v>
+        <v>0.121</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2006</v>
+        <v>-2.7441</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7514</v>
+        <v>0.9505</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4492</v>
+        <v>-3.6946</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3328</v>
+        <v>-3.8816</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3888</v>
+        <v>-1.4805</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9439</v>
+        <v>-2.4011</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6536</v>
+        <v>1.2223</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0205</v>
+        <v>1.1946</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6741</v>
+        <v>0.0276</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6792</v>
+        <v>-5.1038</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4093</v>
+        <v>-2.6751</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2698</v>
+        <v>-2.4287</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9767</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1089</v>
+        <v>1.5717</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.121</v>
+        <v>0.6433</v>
       </c>
       <c r="U9" t="n">
-        <v>0.23</v>
+        <v>0.9284</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.9917</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5893</v>
+        <v>-2.9119</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5248</v>
+        <v>-0.3026</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0645</v>
+        <v>-2.6092</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3251</v>
@@ -1234,13 +1234,13 @@
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.5853</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4345</v>
+        <v>-0.2123</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3423</v>
+        <v>0.7976</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6093</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0347</v>
+        <v>-3.6769</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1675</v>
+        <v>-1.8642</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8672</v>
+        <v>-1.8127</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1352</v>
@@ -1312,13 +1312,13 @@
         <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2196</v>
+        <v>0.1383</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.154</v>
+        <v>0.1493</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0655</v>
+        <v>-0.0111</v>
       </c>
       <c r="V11" t="n">
         <v>1.8828</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.506</v>
+        <v>-5.4515</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3807</v>
+        <v>-2.6529</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1254</v>
+        <v>-2.7986</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7866</v>
@@ -1390,13 +1390,13 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1687</v>
+        <v>-0.1142</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0481</v>
+        <v>-0.3204</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1206</v>
+        <v>0.2062</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9414</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.0626</v>
+        <v>-16.4575</v>
       </c>
       <c r="E13" t="n">
-        <v>3.392799999999998</v>
+        <v>3.9981</v>
       </c>
       <c r="F13" t="n">
         <v>-20.4555</v>
@@ -1468,10 +1468,10 @@
         <v>8.790399999999998</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0222</v>
+        <v>2.6274</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3837999999999999</v>
+        <v>0.2210999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>2.4062</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5404</v>
+        <v>7.9111</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4226</v>
+        <v>7.5237</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1178</v>
+        <v>0.3875</v>
       </c>
       <c r="G14" t="n">
         <v>8.069599999999999</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2091</v>
+        <v>0.1616</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4015</v>
+        <v>-0.3004</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1924</v>
+        <v>0.4621</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8828</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.8369</v>
+        <v>6.776</v>
       </c>
       <c r="E15" t="n">
-        <v>6.097</v>
+        <v>5.7937</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7399</v>
+        <v>0.9823</v>
       </c>
       <c r="G15" t="n">
         <v>3.8593</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1496</v>
+        <v>0.0887</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1432</v>
+        <v>-0.1602</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0065</v>
+        <v>0.2489</v>
       </c>
       <c r="V15" t="n">
         <v>2.4373</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.028</v>
+        <v>6.1924</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7117</v>
+        <v>4.015</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3163</v>
+        <v>2.1774</v>
       </c>
       <c r="G16" t="n">
         <v>4.5062</v>
@@ -1702,13 +1702,13 @@
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0056</v>
+        <v>0.1588</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.4229</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7206</v>
+        <v>0.5817</v>
       </c>
       <c r="V16" t="n">
         <v>0.9414</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1754</v>
+        <v>5.6214</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6846</v>
+        <v>4.8868</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4908</v>
+        <v>0.7346</v>
       </c>
       <c r="G17" t="n">
         <v>3.0422</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2575</v>
+        <v>0.1885</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.22</v>
+        <v>-0.0177</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0376</v>
+        <v>0.2062</v>
       </c>
       <c r="V17" t="n">
         <v>1.2186</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5433</v>
+        <v>3.2515</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0377</v>
+        <v>2.5321</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5056</v>
+        <v>0.7194</v>
       </c>
       <c r="G18" t="n">
         <v>1.5121</v>
@@ -1858,13 +1858,13 @@
         <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6405</v>
+        <v>0.3487</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4404</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2001</v>
+        <v>0.414</v>
       </c>
       <c r="V18" t="n">
         <v>0.6093</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3536</v>
+        <v>0.9403</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1743</v>
+        <v>3.8791</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8207</v>
+        <v>-2.9388</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8903</v>
+        <v>1.3601</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2853</v>
+        <v>-0.6766</v>
       </c>
       <c r="I19" t="n">
-        <v>1.605</v>
+        <v>2.0367</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3558</v>
+        <v>4.0914</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0205</v>
+        <v>0.8404</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3354</v>
+        <v>3.2511</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5344</v>
+        <v>-2.7314</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2648</v>
+        <v>-1.517</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2696</v>
+        <v>-1.2144</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3181</v>
+        <v>-0.2132</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1816</v>
+        <v>-0.4896</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1365</v>
+        <v>0.2764</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>-2.16</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3452</v>
+        <v>0.5636</v>
       </c>
       <c r="E20" t="n">
-        <v>3.4746</v>
+        <v>1.2754</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1294</v>
+        <v>-0.7118</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3601</v>
+        <v>1.8903</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6766</v>
+        <v>0.2853</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0367</v>
+        <v>1.605</v>
       </c>
       <c r="J20" t="n">
-        <v>4.0914</v>
+        <v>1.3558</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8404</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>3.2511</v>
+        <v>1.3354</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7314</v>
+        <v>0.5344</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.517</v>
+        <v>0.2648</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2144</v>
+        <v>0.2696</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8083</v>
+        <v>-0.108</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8941</v>
+        <v>-0.0805</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0858</v>
+        <v>-0.0275</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.16</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4373</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0962</v>
+        <v>-0.4415</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3225</v>
+        <v>-1.0191</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2263</v>
+        <v>0.5777</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9691</v>
@@ -2092,13 +2092,13 @@
         <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7131</v>
+        <v>-0.0584</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3631</v>
+        <v>-0.0598</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.35</v>
+        <v>0.0014</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2176</v>
+        <v>-1.0944</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8512</v>
+        <v>-2.0534</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.959</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2726</v>
@@ -2170,13 +2170,13 @@
         <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0269</v>
+        <v>0.0963</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1899</v>
+        <v>-0.0123</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2168</v>
+        <v>0.1086</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3321</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3322</v>
+        <v>-1.1445</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3617</v>
+        <v>-0.5513</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9705</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4523</v>
+        <v>-0.1176</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7511</v>
+        <v>-0.8729</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.7552</v>
       </c>
       <c r="J23" t="n">
-        <v>1.267</v>
+        <v>1.0506</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1051</v>
+        <v>-0.2443</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1619</v>
+        <v>1.2949</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1852</v>
+        <v>-1.1682</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.354</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5393</v>
+        <v>-0.5397</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
         <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>0.356</v>
+        <v>-0.6362</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3247</v>
+        <v>-0.6252</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0313</v>
+        <v>-0.0111</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4349</v>
+        <v>-1.5266</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6524</v>
+        <v>-0.665</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7825</v>
+        <v>-0.8616</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1176</v>
+        <v>1.4523</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8729</v>
+        <v>0.7511</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7552</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0506</v>
+        <v>1.267</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2443</v>
+        <v>1.1051</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2949</v>
+        <v>0.1619</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1682</v>
+        <v>0.1852</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.354</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5397</v>
+        <v>0.5393</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
         <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9266</v>
+        <v>0.1616</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.0214</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2004</v>
+        <v>0.1402</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.6792</v>
+        <v>-7.9645</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9592</v>
+        <v>-5.1615</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7199</v>
+        <v>-2.803</v>
       </c>
       <c r="G25" t="n">
         <v>-5.776</v>
@@ -2404,13 +2404,13 @@
         <v>0.1953</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0968</v>
+        <v>-0.1885</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0083</v>
+        <v>-0.1939</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0885</v>
+        <v>0.0054</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2186</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>17.0627</v>
+        <v>19.0848</v>
       </c>
       <c r="E26" t="n">
         <v>20.4555</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.3927</v>
+        <v>-1.370500000000001</v>
       </c>
       <c r="G26" t="n">
         <v>18.5568</v>
@@ -2464,7 +2464,7 @@
         <v>11.4716</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.3856</v>
+        <v>-8.385599999999998</v>
       </c>
       <c r="N26" t="n">
         <v>-6.358099999999999</v>
@@ -2473,7 +2473,7 @@
         <v>-2.0274</v>
       </c>
       <c r="P26" t="n">
-        <v>3.9068</v>
+        <v>3.906799999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-8.7903</v>
@@ -2482,13 +2482,13 @@
         <v>12.6972</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0223</v>
+        <v>-9.999999999996123e-05</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.4064</v>
+        <v>-2.4063</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3839</v>
+        <v>2.4063</v>
       </c>
       <c r="V26" t="n">
         <v>-3.3786</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484235_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484235_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +570,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6944</v>
+        <v>1.5349</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7596</v>
+        <v>1.5349</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0652</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.499</v>
+        <v>1.5349</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7693</v>
+        <v>1.5349</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2702</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6577</v>
+        <v>1.5349</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6577</v>
+        <v>1.5349</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1587</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8885</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2702</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1018</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4925</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -626,12 +631,17 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2216</v>
+        <v>0.6944</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0013</v>
+        <v>1.7596</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2203</v>
+        <v>-1.0652</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3173</v>
+        <v>0.499</v>
       </c>
       <c r="H3" t="n">
-        <v>0.142</v>
+        <v>0.7693</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1753</v>
+        <v>-0.2702</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1223</v>
+        <v>1.6577</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0819</v>
+        <v>1.6577</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1949</v>
+        <v>-1.1587</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0601</v>
+        <v>-0.8885</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1348</v>
+        <v>-0.2702</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0138</v>
+        <v>-0.3907</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.121</v>
+        <v>0.1018</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1073</v>
+        <v>-0.4925</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2111</v>
+        <v>0.2216</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6635</v>
+        <v>0.0013</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4524</v>
+        <v>0.2203</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0714</v>
+        <v>0.3173</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.142</v>
       </c>
       <c r="I4" t="n">
-        <v>0.998</v>
+        <v>0.1753</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6395</v>
+        <v>0.1223</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9424</v>
+        <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.568</v>
+        <v>0.1949</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6237</v>
+        <v>0.0601</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9443</v>
+        <v>0.1348</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1396</v>
+        <v>-0.0138</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007</v>
+        <v>-0.121</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1389</v>
+        <v>0.1073</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0382</v>
+        <v>0.2111</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3623</v>
+        <v>1.6635</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.3241</v>
+        <v>-1.4524</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6729</v>
+        <v>1.0714</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8634</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8095</v>
+        <v>0.998</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5708</v>
+        <v>2.6395</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6817</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8891</v>
+        <v>1.9424</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.2437</v>
+        <v>-1.568</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.5451</v>
+        <v>-0.6237</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.6986</v>
+        <v>-0.9443</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8832</v>
+        <v>0.1396</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2258</v>
+        <v>0.0007</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6574</v>
+        <v>0.1389</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8279</v>
+        <v>-0.6093</v>
       </c>
       <c r="W5" t="n">
-        <v>4.5424</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7145</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1008</v>
+        <v>0.0382</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0237</v>
+        <v>6.3623</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1246</v>
+        <v>-6.3241</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5266</v>
+        <v>-2.6729</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2829</v>
+        <v>-1.8634</v>
       </c>
       <c r="I6" t="n">
         <v>-0.8095</v>
       </c>
       <c r="J6" t="n">
-        <v>0.023</v>
+        <v>2.5708</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.6817</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6741</v>
+        <v>1.8891</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5496</v>
+        <v>-5.2437</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4142</v>
+        <v>-2.5451</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1354</v>
+        <v>-2.6986</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3556</v>
+        <v>0.8832</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0007</v>
+        <v>0.2258</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3564</v>
+        <v>0.6574</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.5424</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6303</v>
+        <v>-0.1008</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3939</v>
+        <v>0.0237</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2363</v>
+        <v>-0.1246</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7838</v>
+        <v>-0.5266</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2978</v>
+        <v>0.2829</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.486</v>
+        <v>-0.8095</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.066</v>
+        <v>0.023</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1203</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0543</v>
+        <v>-0.6741</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7178</v>
+        <v>-0.5496</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1775</v>
+        <v>-0.4142</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5403</v>
+        <v>-0.1354</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0186</v>
+        <v>-0.3556</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.328</v>
+        <v>0.0007</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3094</v>
+        <v>-0.3564</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1073</v>
+        <v>-0.6303</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5492</v>
+        <v>-0.3939</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5581</v>
+        <v>-0.2363</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3328</v>
+        <v>-1.7838</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3888</v>
+        <v>-1.2978</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9439</v>
+        <v>-0.486</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6536</v>
+        <v>-0.066</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205</v>
+        <v>-0.1203</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6741</v>
+        <v>0.0543</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6792</v>
+        <v>-1.7178</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4093</v>
+        <v>-1.1775</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2698</v>
+        <v>-0.5403</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2022</v>
+        <v>-0.0186</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.328</v>
       </c>
       <c r="U8" t="n">
-        <v>0.121</v>
+        <v>0.3094</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,12 +1129,17 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7441</v>
+        <v>-2.1073</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9505</v>
+        <v>-1.5492</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.6946</v>
+        <v>-0.5581</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8816</v>
+        <v>-1.3328</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4805</v>
+        <v>-0.3888</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.4011</v>
+        <v>-0.9439</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2223</v>
+        <v>-0.6536</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1946</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0276</v>
+        <v>-0.6741</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.1038</v>
+        <v>-0.6792</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6751</v>
+        <v>-0.4093</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4287</v>
+        <v>-0.2698</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.5395</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5717</v>
+        <v>0.2022</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6433</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9284</v>
+        <v>0.121</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9917</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9119</v>
+        <v>-2.7441</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3026</v>
+        <v>0.9505</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6092</v>
+        <v>-3.6946</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3251</v>
+        <v>-3.8816</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7096</v>
+        <v>-1.4805</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0347</v>
+        <v>-2.4011</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8399</v>
+        <v>1.2223</v>
       </c>
       <c r="K10" t="n">
-        <v>4.12</v>
+        <v>1.1946</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2801</v>
+        <v>0.0276</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.165</v>
+        <v>-5.1038</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.4103</v>
+        <v>-2.6751</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7546</v>
+        <v>-2.4287</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5627</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5853</v>
+        <v>1.5717</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2123</v>
+        <v>0.6433</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7976</v>
+        <v>0.9284</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6093</v>
+        <v>2.1052</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.9917</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6093</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6769</v>
+        <v>-2.9119</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8642</v>
+        <v>-0.3026</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8127</v>
+        <v>-2.6092</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1352</v>
+        <v>-1.3251</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.5416</v>
+        <v>1.7096</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5936</v>
+        <v>-3.0347</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2787</v>
+        <v>2.8399</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8995</v>
+        <v>4.12</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6208</v>
+        <v>-1.2801</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8565</v>
+        <v>-4.165</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6421</v>
+        <v>-2.4103</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2144</v>
+        <v>-1.7546</v>
       </c>
       <c r="P11" t="n">
         <v>-1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1383</v>
+        <v>0.5853</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1493</v>
+        <v>-0.2123</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0111</v>
+        <v>0.7976</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8828</v>
+        <v>-0.6093</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6642</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4515</v>
+        <v>-3.6769</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6529</v>
+        <v>-1.8642</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7986</v>
+        <v>-1.8127</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.7866</v>
+        <v>-4.1352</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.5176</v>
+        <v>-3.5416</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.269</v>
+        <v>-0.5936</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6917</v>
+        <v>-1.2787</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7726</v>
+        <v>-1.8995</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>0.6208</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.0949</v>
+        <v>-2.8565</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.7449</v>
+        <v>-1.6421</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.35</v>
+        <v>-1.2144</v>
       </c>
       <c r="P12" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.3907</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3674</v>
-      </c>
       <c r="S12" t="n">
-        <v>-0.1142</v>
+        <v>0.1383</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3204</v>
+        <v>0.1493</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2062</v>
+        <v>-0.0111</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9414</v>
+        <v>1.8828</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.4575</v>
+        <v>-6.9864</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9981</v>
+        <v>-4.1878</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.4555</v>
+        <v>-2.7986</v>
       </c>
       <c r="G13" t="n">
-        <v>-18.5569</v>
+        <v>-6.3215</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.112500000000001</v>
+        <v>-5.0525</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.444199999999999</v>
+        <v>-1.269</v>
       </c>
       <c r="J13" t="n">
-        <v>8.3855</v>
+        <v>-2.2266</v>
       </c>
       <c r="K13" t="n">
-        <v>6.358200000000001</v>
+        <v>-2.3075</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0273</v>
+        <v>0.0809</v>
       </c>
       <c r="M13" t="n">
-        <v>-26.9423</v>
+        <v>-4.0949</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.4706</v>
+        <v>-2.7449</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.4715</v>
+        <v>-1.35</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.9068</v>
+        <v>0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6972</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>8.790399999999998</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6274</v>
+        <v>-0.1142</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2210999999999999</v>
+        <v>-0.3204</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4062</v>
+        <v>0.2062</v>
       </c>
       <c r="V13" t="n">
-        <v>3.3787</v>
+        <v>-0.9414</v>
       </c>
       <c r="W13" t="n">
-        <v>8.0885</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.7098</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.9111</v>
+        <v>-16.4575</v>
       </c>
       <c r="E14" t="n">
-        <v>7.5237</v>
+        <v>3.9981</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3875</v>
+        <v>-20.4555</v>
       </c>
       <c r="G14" t="n">
-        <v>8.069599999999999</v>
+        <v>-18.5569</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6821</v>
+        <v>-9.112500000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3875</v>
+        <v>-9.444199999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>9.1877</v>
+        <v>8.3855</v>
       </c>
       <c r="K14" t="n">
-        <v>6.5298</v>
+        <v>6.358200000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6579</v>
+        <v>2.0273</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1182</v>
+        <v>-26.9423</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8478</v>
+        <v>-15.4706</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2704</v>
+        <v>-11.4715</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>-3.9068</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-12.6972</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>8.7904</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1616</v>
+        <v>2.6274</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3004</v>
+        <v>0.2211000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4621</v>
+        <v>2.4062</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.8828</v>
+        <v>3.3787</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3869</v>
+        <v>8.0885</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
-      </c>
+        <v>-4.7098</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.776</v>
+        <v>7.2972</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7937</v>
+        <v>6.9097</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9823</v>
+        <v>0.3875</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8593</v>
+        <v>7.4556</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9553</v>
+        <v>5.0681</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9041</v>
+        <v>2.3875</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4933</v>
+        <v>8.5738</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0494</v>
+        <v>5.9159</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4439</v>
+        <v>2.6579</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.634</v>
+        <v>-1.1182</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0941</v>
+        <v>-0.8478</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5399</v>
+        <v>-0.2704</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0887</v>
+        <v>0.1616</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1602</v>
+        <v>-0.3004</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2489</v>
+        <v>0.4621</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4373</v>
+        <v>-1.8828</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4373</v>
+        <v>-0.3869</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1924</v>
+        <v>6.469</v>
       </c>
       <c r="E16" t="n">
-        <v>4.015</v>
+        <v>5.4867</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1774</v>
+        <v>0.9823</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5062</v>
+        <v>3.5524</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8215</v>
+        <v>2.6483</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6848</v>
+        <v>0.9041</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8054</v>
+        <v>4.1863</v>
       </c>
       <c r="K16" t="n">
-        <v>2.255</v>
+        <v>2.7424</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5503</v>
+        <v>1.4439</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2992</v>
+        <v>-0.634</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4336</v>
+        <v>-0.0941</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1344</v>
+        <v>-0.5399</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1588</v>
+        <v>0.0887</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4229</v>
+        <v>-0.1602</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5817</v>
+        <v>0.2489</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9414</v>
+        <v>2.4373</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6093</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6214</v>
+        <v>6.1924</v>
       </c>
       <c r="E17" t="n">
-        <v>4.8868</v>
+        <v>4.015</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7346</v>
+        <v>2.1774</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0422</v>
+        <v>4.5062</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0051</v>
+        <v>1.8215</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0371</v>
+        <v>2.6848</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6859</v>
+        <v>4.8054</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7831</v>
+        <v>2.255</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9029</v>
+        <v>2.5503</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6437</v>
+        <v>-0.2992</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7779</v>
+        <v>-0.4336</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1342</v>
+        <v>0.1344</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1885</v>
+        <v>0.1588</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0177</v>
+        <v>-0.4229</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2062</v>
+        <v>0.5817</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2186</v>
+        <v>0.9414</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.2515</v>
+        <v>5.6214</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5321</v>
+        <v>4.8868</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7194</v>
+        <v>0.7346</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5121</v>
+        <v>3.0422</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6744</v>
+        <v>1.0051</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1623</v>
+        <v>2.0371</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9647</v>
+        <v>3.6859</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7219</v>
+        <v>1.7831</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2428</v>
+        <v>1.9029</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4526</v>
+        <v>-0.6437</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0476</v>
+        <v>-0.7779</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4051</v>
+        <v>0.1342</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3487</v>
+        <v>0.1885</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0177</v>
       </c>
       <c r="U18" t="n">
-        <v>0.414</v>
+        <v>0.2062</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9403</v>
+        <v>3.2515</v>
       </c>
       <c r="E19" t="n">
-        <v>3.8791</v>
+        <v>2.5321</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9388</v>
+        <v>0.7194</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3601</v>
+        <v>1.5121</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6766</v>
+        <v>1.6744</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0367</v>
+        <v>-0.1623</v>
       </c>
       <c r="J19" t="n">
-        <v>4.0914</v>
+        <v>2.9647</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8404</v>
+        <v>2.7219</v>
       </c>
       <c r="L19" t="n">
-        <v>3.2511</v>
+        <v>0.2428</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7314</v>
+        <v>-1.4526</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.517</v>
+        <v>-1.0476</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2144</v>
+        <v>-0.4051</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2132</v>
+        <v>0.3487</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4896</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2764</v>
+        <v>0.414</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.16</v>
+        <v>0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5636</v>
+        <v>0.9403</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2754</v>
+        <v>3.8791</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7118</v>
+        <v>-2.9388</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8903</v>
+        <v>1.3601</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2853</v>
+        <v>-0.6766</v>
       </c>
       <c r="I20" t="n">
-        <v>1.605</v>
+        <v>2.0367</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3558</v>
+        <v>4.0914</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0205</v>
+        <v>0.8404</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3354</v>
+        <v>3.2511</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5344</v>
+        <v>-2.7314</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2648</v>
+        <v>-1.517</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2696</v>
+        <v>-1.2144</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.108</v>
+        <v>-0.2132</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0805</v>
+        <v>-0.4896</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0275</v>
+        <v>0.2764</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>-2.16</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4415</v>
+        <v>0.614</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0191</v>
+        <v>0.614</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5777</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9691</v>
+        <v>0.614</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4298</v>
+        <v>0.614</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5393</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9594</v>
+        <v>0.614</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2853</v>
+        <v>0.614</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0097</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1445</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0584</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0598</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0014</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2108,12 +2204,17 @@
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2226,72 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0944</v>
+        <v>0.5636</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0534</v>
+        <v>1.2754</v>
       </c>
       <c r="F22" t="n">
-        <v>0.959</v>
+        <v>-0.7118</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2726</v>
+        <v>1.8903</v>
       </c>
       <c r="H22" t="n">
-        <v>0.077</v>
+        <v>0.2853</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3496</v>
+        <v>1.605</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7323</v>
+        <v>1.3558</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0217</v>
+        <v>0.0205</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.754</v>
+        <v>1.3354</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4597</v>
+        <v>0.5344</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0553</v>
+        <v>0.2648</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4045</v>
+        <v>0.2696</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0963</v>
+        <v>-0.108</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0123</v>
+        <v>-0.0805</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1086</v>
+        <v>-0.0275</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1445</v>
+        <v>0.307</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5513</v>
+        <v>0.307</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1176</v>
+        <v>0.307</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8729</v>
+        <v>0.307</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7552</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0506</v>
+        <v>0.307</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2443</v>
+        <v>0.307</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2949</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1682</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5397</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6362</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6252</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0111</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5266</v>
+        <v>0.307</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.665</v>
+        <v>0.307</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8616</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4523</v>
+        <v>0.307</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7511</v>
+        <v>0.307</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7010999999999999</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1.267</v>
+        <v>0.307</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1051</v>
+        <v>0.307</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1619</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1852</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.354</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5393</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1616</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0214</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1402</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.9645</v>
+        <v>-0.4415</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1615</v>
+        <v>-1.0191</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.803</v>
+        <v>0.5777</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.776</v>
+        <v>-0.9691</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.1599</v>
+        <v>-0.4298</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.6161</v>
+        <v>-0.5393</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.2681</v>
+        <v>-0.9594</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.3267</v>
+        <v>-0.2853</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9414</v>
+        <v>-0.6741</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5079</v>
+        <v>-0.0097</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.1445</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6747</v>
+        <v>0.1348</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1885</v>
+        <v>-0.0584</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1939</v>
+        <v>-0.0598</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0054</v>
+        <v>0.0014</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,401 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>19.0848</v>
+        <v>-1.0944</v>
       </c>
       <c r="E26" t="n">
+        <v>-2.0534</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.2726</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.3496</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.7323</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.754</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4597</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P. MARTINEZ FERIA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.4515</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.8583</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.5931999999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.4246</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.1798</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7552</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7436</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.5513</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.2949</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.1682</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.6284999999999999</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.5397</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.6362</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.6252</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>U. FERNANDEZ RUIZ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.5266</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.665</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.8616</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.4523</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7511</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7010999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.1051</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.354</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>F. LLORENS LLAURADO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-7.9645</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-5.1615</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-2.803</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-5.776</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-3.1599</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-2.6161</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-4.2681</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-2.3267</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-1.9414</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-1.5079</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-0.8332000000000001</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.6747</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-0.1885</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.1939</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>play_by_play_2484235_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>19.0849</v>
+      </c>
+      <c r="E30" t="n">
         <v>20.4555</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F30" t="n">
         <v>-1.370500000000001</v>
       </c>
-      <c r="G26" t="n">
-        <v>18.5568</v>
-      </c>
-      <c r="H26" t="n">
-        <v>9.112599999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>9.444200000000002</v>
-      </c>
-      <c r="J26" t="n">
-        <v>26.942</v>
-      </c>
-      <c r="K26" t="n">
-        <v>15.4706</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="G30" t="n">
+        <v>18.55689999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>9.112699999999998</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.4442</v>
+      </c>
+      <c r="J30" t="n">
+        <v>26.9421</v>
+      </c>
+      <c r="K30" t="n">
+        <v>15.4707</v>
+      </c>
+      <c r="L30" t="n">
         <v>11.4716</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M30" t="n">
         <v>-8.385599999999998</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N30" t="n">
         <v>-6.358099999999999</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O30" t="n">
         <v>-2.0274</v>
       </c>
-      <c r="P26" t="n">
-        <v>3.906799999999999</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="P30" t="n">
+        <v>3.9068</v>
+      </c>
+      <c r="Q30" t="n">
         <v>-8.7903</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R30" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S26" t="n">
-        <v>-9.999999999996123e-05</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="S30" t="n">
+        <v>-0.0001000000000001833</v>
+      </c>
+      <c r="T30" t="n">
         <v>-2.4063</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U30" t="n">
         <v>2.4063</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V30" t="n">
         <v>-3.3786</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W30" t="n">
         <v>4.709899999999999</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X30" t="n">
         <v>-8.088700000000001</v>
       </c>
+      <c r="Y30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
